--- a/experiment1/data_processing3/exp_data/11_merged_initTime_for_ANCOVA.xlsx
+++ b/experiment1/data_processing3/exp_data/11_merged_initTime_for_ANCOVA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:BE42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,191 @@
           <t>mean_initiation_time</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>gaze_effect_cons</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>gaze_effect_incons</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>gaze_effect_ctrl</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>mean_initiation_time_centered</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>d_cons</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>d_incons</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>d_ctrl</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>cong_cons_bin1</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>cong_cons_bin2</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>cong_cons_bin3</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>cong_cons_bin4</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>cong_cons_bin5</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>cong_incons_bin1</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>cong_incons_bin2</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>cong_incons_bin3</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>cong_incons_bin4</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>cong_incons_bin5</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>cong_ctrl_bin1</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>cong_ctrl_bin2</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>cong_ctrl_bin3</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>cong_ctrl_bin4</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>cong_ctrl_bin5</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>incong_cons_bin1</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>incong_cons_bin2</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>incong_cons_bin3</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>incong_cons_bin4</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>incong_cons_bin5</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>incong_incons_bin1</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>incong_incons_bin2</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>incong_incons_bin3</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>incong_incons_bin4</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>incong_incons_bin5</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>incong_ctrl_bin1</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>incong_ctrl_bin2</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>incong_ctrl_bin3</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>incong_ctrl_bin4</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>incong_ctrl_bin5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -583,6 +768,117 @@
       <c r="T2" t="n">
         <v>321.6530612244898</v>
       </c>
+      <c r="U2" t="n">
+        <v>26</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>21</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-194.2730422939806</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.365881226703204</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1001428047756501</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2493147224036435</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>460</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>522</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>416.3333333333333</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>440.6666666666667</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>473.3333333333333</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>515.75</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>313.3333333333333</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>429</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>477</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>563.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>402</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>428.25</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>485</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>559.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>341</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>396.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>440.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>498.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>572.1666666666666</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>358.8333333333333</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>400.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>438</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>508.6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>563</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -649,6 +945,117 @@
       <c r="T3" t="n">
         <v>405.5596330275229</v>
       </c>
+      <c r="U3" t="n">
+        <v>33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-110.3664704909475</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.48450649724342</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.1141961124719839</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.2049820338522598</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>397.8333333333333</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>464.6666666666667</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>489</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>536</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>597.8333333333334</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>488</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>532.6666666666666</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>559.25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>618.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>383</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>430.2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>499</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>544.6666666666666</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>456</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>522.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>613.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>447</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>486.3333333333333</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>512.6666666666666</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>544</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>602.2857142857143</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>374.1666666666667</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>434.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>479.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>507</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>609.6666666666666</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -715,6 +1122,117 @@
       <c r="T4" t="n">
         <v>439.3714285714286</v>
       </c>
+      <c r="U4" t="n">
+        <v>62</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-76.5546749470418</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5255053920442821</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.2822022130376896</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.08458128076245128</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>394</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>495.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>512.25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>543</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>670.4</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>448.3333333333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>512.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>556.3333333333334</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>610.8</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>805.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>387.3333333333333</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>475.4</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>526.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>576.6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>737.3333333333334</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>502.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>553.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>646</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>772</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>459.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>506.75</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>528</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>568.75</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>702.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>506</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>544.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>608.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>725.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -781,6 +1299,117 @@
       <c r="T5" t="n">
         <v>282.46</v>
       </c>
+      <c r="U5" t="n">
+        <v>45</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>99</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-233.4661035184704</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.5051127760823304</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.01987471702662929</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.144675061845962</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>433.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>475</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>549.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>603.2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>478.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>562</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>593.75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>631</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>733.25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>406.1666666666667</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>523.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>577.2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>659</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>420.8333333333333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>516.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>573</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>615.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>705.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>455</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>557.6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>586.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>640.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>721.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>544.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>573.25</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>613.25</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>676</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>736.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -847,55 +1476,166 @@
       <c r="T6" t="n">
         <v>579.7326732673267</v>
       </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>74</v>
+      </c>
+      <c r="X6" t="n">
+        <v>63.8065697488563</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.006359098273149785</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1960385112384251</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.6415733625633142</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>396</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>441</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>476.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>561.8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>284</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>437.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>465.4</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>509.8333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>323</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>364</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>441</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>482.4</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>313.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>396</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>421.75</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>499</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>582.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>311.8</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>388</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>430.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>468</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>550.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>491.25</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>602.25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>716</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>433.1428571428572</v>
+        <v>681</v>
       </c>
       <c r="C7" t="n">
-        <v>440</v>
+        <v>709.52</v>
       </c>
       <c r="D7" t="n">
-        <v>406.84</v>
+        <v>723.4400000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>462.0416666666667</v>
+        <v>693.25</v>
       </c>
       <c r="F7" t="n">
-        <v>440.5185185185185</v>
+        <v>710.0769230769231</v>
       </c>
       <c r="G7" t="n">
-        <v>432.962962962963</v>
+        <v>664.5769230769231</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6875</v>
+        <v>3.625</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6875</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6.375</v>
+        <v>4.0625</v>
       </c>
       <c r="K7" t="n">
-        <v>1.25</v>
+        <v>1.4375</v>
       </c>
       <c r="L7" t="n">
-        <v>1.375</v>
+        <v>1.125</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9375</v>
+        <v>1.4375</v>
       </c>
       <c r="N7" t="n">
-        <v>6.9375</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.125</v>
+        <v>2.9375</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1875</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>19</v>
@@ -911,57 +1651,168 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>396.688679245283</v>
+        <v>522.5135135135135</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-59</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>6.587409995043117</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1019497519195203</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.4292750340030465</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.003863576230215707</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>518.6666666666666</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>625.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>680</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>742.4</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>870.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>565</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>650.6</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>709.6</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>751.4</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>940.6</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>520.8</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>659.8</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>722</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>764.4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>880.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>556.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>637.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>688.75</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>721.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>860.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>581.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>662.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>775.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>850</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>523</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>630.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>693.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>811.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>929.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>493.8571428571428</v>
+        <v>433.1428571428572</v>
       </c>
       <c r="C8" t="n">
-        <v>522.6296296296297</v>
+        <v>440</v>
       </c>
       <c r="D8" t="n">
-        <v>533.5666666666667</v>
+        <v>406.84</v>
       </c>
       <c r="E8" t="n">
-        <v>520.0645161290323</v>
+        <v>462.0416666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>516.28</v>
+        <v>440.5185185185185</v>
       </c>
       <c r="G8" t="n">
-        <v>528.375</v>
+        <v>432.962962962963</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1875</v>
+        <v>6.6875</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9375</v>
+        <v>1.6875</v>
       </c>
       <c r="J8" t="n">
-        <v>4.875</v>
+        <v>6.375</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>4.9375</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>6.9375</v>
       </c>
       <c r="O8" t="n">
-        <v>3.625</v>
+        <v>1.125</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>1.1875</v>
       </c>
       <c r="Q8" t="n">
         <v>19</v>
@@ -977,64 +1828,175 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>355.6964285714286</v>
+        <v>396.688679245283</v>
+      </c>
+      <c r="U8" t="n">
+        <v>29</v>
+      </c>
+      <c r="V8" t="n">
+        <v>26</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-119.2374242731874</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3338280948297022</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.3838141488695498</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.005288753924489207</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>346.1666666666667</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>409.1666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>468.6</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>553.1666666666666</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>305.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>412.4</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>442.6</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>505</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>404.25</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>468.4</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>622.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>399.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>439.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>499.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>611.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>356.3333333333333</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>398</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>455.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>532.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>434.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>474.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>562.3333333333334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>477.962962962963</v>
+        <v>493.8571428571428</v>
       </c>
       <c r="C9" t="n">
-        <v>533.8461538461538</v>
+        <v>522.6296296296297</v>
       </c>
       <c r="D9" t="n">
-        <v>457.68</v>
+        <v>533.5666666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>484.8</v>
+        <v>520.0645161290323</v>
       </c>
       <c r="F9" t="n">
-        <v>521.5454545454545</v>
+        <v>516.28</v>
       </c>
       <c r="G9" t="n">
-        <v>499.3703703703704</v>
+        <v>528.375</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9375</v>
+        <v>6.1875</v>
       </c>
       <c r="I9" t="n">
-        <v>3.875</v>
+        <v>5.9375</v>
       </c>
       <c r="J9" t="n">
-        <v>3.875</v>
+        <v>4.875</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6875</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9375</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5625</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4375</v>
+        <v>3.625</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1043,64 +2005,175 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>423.4234234234234</v>
+        <v>355.6964285714286</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-160.2296749470418</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4220933905326501</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.08104657725075923</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.0886897052437403</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>434.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>470</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>504.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>525.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>549.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>452.3333333333333</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>483.6666666666667</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>529</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>571.1666666666666</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>631.6666666666666</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>440.6666666666667</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>487.8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>517</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>548.4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>616.8333333333334</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>442.2857142857143</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>478</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>508.3333333333333</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>551.3333333333334</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>633.3333333333334</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>453</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>489.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>524</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>558.8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>615.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>478.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>506</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>547.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>628</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>531.52</v>
+        <v>477.962962962963</v>
       </c>
       <c r="C10" t="n">
-        <v>631.625</v>
+        <v>533.8461538461538</v>
       </c>
       <c r="D10" t="n">
-        <v>534.2083333333334</v>
+        <v>457.68</v>
       </c>
       <c r="E10" t="n">
-        <v>562.16</v>
+        <v>484.8</v>
       </c>
       <c r="F10" t="n">
-        <v>651.16</v>
+        <v>521.5454545454545</v>
       </c>
       <c r="G10" t="n">
-        <v>561.7307692307693</v>
+        <v>499.3703703703704</v>
       </c>
       <c r="H10" t="n">
-        <v>6.75</v>
+        <v>3.9375</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4375</v>
+        <v>3.875</v>
       </c>
       <c r="J10" t="n">
-        <v>6.8125</v>
+        <v>3.875</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2.6875</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>1.9375</v>
       </c>
       <c r="N10" t="n">
         <v>3.5625</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>3.4375</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6875</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1109,60 +2182,171 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>682</v>
+        <v>423.4234234234234</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>42</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-92.50268009504703</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.05843531913600826</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.3732473815440074</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.09190844793797104</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>343.8333333333333</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>414.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>471.4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>517.6</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>637.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>455.2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>515.6</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>597.6</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>441</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>546</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>620.6</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>721.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>487.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>569</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>650.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>360.1666666666667</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>416.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>465.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>570.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>676.1666666666666</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>387</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>438.75</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>493.25</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>560</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>714.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
-        <v>526.72</v>
+        <v>540.4583333333334</v>
       </c>
       <c r="C11" t="n">
-        <v>564.88</v>
+        <v>631.625</v>
       </c>
       <c r="D11" t="n">
-        <v>522.9230769230769</v>
+        <v>534.2083333333334</v>
       </c>
       <c r="E11" t="n">
-        <v>598.36</v>
+        <v>562.16</v>
       </c>
       <c r="F11" t="n">
-        <v>568.76</v>
+        <v>651.16</v>
       </c>
       <c r="G11" t="n">
-        <v>560.9642857142857</v>
+        <v>561.7307692307693</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1875</v>
+        <v>6.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.125</v>
+        <v>6.4375</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0625</v>
+        <v>6.8125</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3125</v>
+        <v>3.5625</v>
       </c>
       <c r="O11" t="n">
-        <v>3.875</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8125</v>
+        <v>1.6875</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1175,42 +2359,153 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>326.5090909090909</v>
+        <v>682</v>
+      </c>
+      <c r="U11" t="n">
+        <v>22</v>
+      </c>
+      <c r="V11" t="n">
+        <v>28</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20</v>
+      </c>
+      <c r="X11" t="n">
+        <v>166.0738964815296</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.2230054641318265</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.235443655704142</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1171258149741431</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>418.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>484.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>546.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>594.4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>659.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>402</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>485</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>529.75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>578</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>675.4</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>438</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>530.6</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>700.2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>869.8</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>410.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>532.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>567.8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>599.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>701</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>407.8333333333333</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>496.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>553</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>620.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>762</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>440.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>627.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>708.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>927.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>548.5454545454545</v>
+        <v>526.72</v>
       </c>
       <c r="C12" t="n">
-        <v>494.7</v>
+        <v>564.88</v>
       </c>
       <c r="D12" t="n">
-        <v>527.8421052631579</v>
+        <v>522.9230769230769</v>
       </c>
       <c r="E12" t="n">
-        <v>525.4814814814815</v>
+        <v>598.36</v>
       </c>
       <c r="F12" t="n">
-        <v>536.4347826086956</v>
+        <v>568.76</v>
       </c>
       <c r="G12" t="n">
-        <v>555.4193548387096</v>
+        <v>560.9642857142857</v>
       </c>
       <c r="H12" t="n">
-        <v>6.625</v>
+        <v>3.1875</v>
       </c>
       <c r="I12" t="n">
-        <v>6.625</v>
+        <v>4.125</v>
       </c>
       <c r="J12" t="n">
-        <v>5.875</v>
+        <v>3.0625</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>1.1875</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1219,16 +2514,16 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3.3125</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>3.875</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2.8125</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1241,42 +2536,153 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>380.3461538461539</v>
+        <v>326.5090909090909</v>
+      </c>
+      <c r="U12" t="n">
+        <v>72</v>
+      </c>
+      <c r="V12" t="n">
+        <v>38</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-189.4170126093795</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.7647005341020641</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.3642335128027799</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.04272704112919675</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>429.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>497</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>527.6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>567.8</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>611.6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>402.1666666666667</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>493.2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>517.2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>569.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>657</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>423.6</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>507.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>556.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>627.2</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>709.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>454.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>538</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>583.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>645</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>770.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>429.1666666666667</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>497</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>539.3333333333334</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>602.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>733.3333333333334</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>460.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>527</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>575.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>617.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>663.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="n">
-        <v>612.16</v>
+        <v>548.5454545454545</v>
       </c>
       <c r="C13" t="n">
-        <v>648.84</v>
+        <v>494.7</v>
       </c>
       <c r="D13" t="n">
-        <v>558.6666666666666</v>
+        <v>527.8421052631579</v>
       </c>
       <c r="E13" t="n">
-        <v>569.4782608695652</v>
+        <v>525.4814814814815</v>
       </c>
       <c r="F13" t="n">
-        <v>672.2727272727273</v>
+        <v>536.4347826086956</v>
       </c>
       <c r="G13" t="n">
-        <v>582.2272727272727</v>
+        <v>555.4193548387096</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4375</v>
+        <v>6.625</v>
       </c>
       <c r="I13" t="n">
-        <v>1.25</v>
+        <v>6.625</v>
       </c>
       <c r="J13" t="n">
-        <v>1.125</v>
+        <v>5.875</v>
       </c>
       <c r="K13" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1285,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>6.625</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1307,64 +2713,175 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>707.77</v>
+        <v>380.3461538461539</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-23</v>
+      </c>
+      <c r="V13" t="n">
+        <v>28</v>
+      </c>
+      <c r="W13" t="n">
+        <v>42</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-135.5799496723165</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.1951284712127549</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.2439966848583349</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.396391347819907</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>413.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>483.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>525.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>591.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>720</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>401</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>462.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>502</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>567.25</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>700.25</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>438</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>482.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>648.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>459.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>503.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>597.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>686.6666666666666</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>423.1428571428572</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>494.6666666666667</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>602</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>740.8333333333334</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>394.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>476</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>538.2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>599.25</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>674.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="n">
-        <v>381.5</v>
+        <v>612.16</v>
       </c>
       <c r="C14" t="n">
-        <v>393.5925925925926</v>
+        <v>648.84</v>
       </c>
       <c r="D14" t="n">
-        <v>378.92</v>
+        <v>558.6666666666666</v>
       </c>
       <c r="E14" t="n">
-        <v>411.5925925925926</v>
+        <v>569.4782608695652</v>
       </c>
       <c r="F14" t="n">
-        <v>420.5</v>
+        <v>672.2727272727273</v>
       </c>
       <c r="G14" t="n">
-        <v>389.6538461538461</v>
+        <v>582.2272727272727</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1875</v>
+        <v>6.4375</v>
       </c>
       <c r="I14" t="n">
-        <v>5.0625</v>
+        <v>1.25</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0625</v>
+        <v>1.125</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0625</v>
+        <v>6.625</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3125</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>22</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1373,130 +2890,352 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>249.1588785046729</v>
+        <v>707.77</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-43</v>
+      </c>
+      <c r="V14" t="n">
+        <v>24</v>
+      </c>
+      <c r="W14" t="n">
+        <v>23</v>
+      </c>
+      <c r="X14" t="n">
+        <v>191.8438964815296</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.2953867980405033</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.1396201642966001</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.1190551116514546</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>446</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>525.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>583</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>681</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>825</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>354</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>476.4</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>535</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>637</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>786.2</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>508.8</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>605</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>724.4</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>986.8</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>482.25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>541.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>656.25</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>775.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>409.6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>460.25</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>532.75</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>625</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>857.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>561.25</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>608</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>760</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>943</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B15" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>393.5925925925926</v>
+      </c>
+      <c r="D15" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="E15" t="n">
+        <v>411.5925925925926</v>
+      </c>
+      <c r="F15" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>389.6538461538461</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.1875</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.0625</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.0625</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>22</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>249.1588785046729</v>
+      </c>
+      <c r="U15" t="n">
+        <v>30</v>
+      </c>
+      <c r="V15" t="n">
+        <v>11</v>
+      </c>
+      <c r="W15" t="n">
         <v>27</v>
       </c>
-      <c r="B15" t="n">
-        <v>503.6956521739131</v>
-      </c>
-      <c r="C15" t="n">
-        <v>585.3076923076923</v>
-      </c>
-      <c r="D15" t="n">
-        <v>507.2608695652174</v>
-      </c>
-      <c r="E15" t="n">
-        <v>477.0869565217391</v>
-      </c>
-      <c r="F15" t="n">
-        <v>560.6799999999999</v>
-      </c>
-      <c r="G15" t="n">
-        <v>483.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>6.1875</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.3125</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.8125</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.875</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>28</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>1365.616161616162</v>
+      <c r="X15" t="n">
+        <v>-266.7672250137975</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4907820217344082</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.2139396869694276</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.4745753546380227</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>302</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>386</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>448</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>397</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>452.6</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>310.8333333333333</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>394</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>431</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>330.8333333333333</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>371</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>399</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>439.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>332.8333333333333</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>354</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>432.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>354.3333333333333</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>404</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>420.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>440.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>496.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" t="n">
-        <v>384.5555555555555</v>
+        <v>503.6956521739131</v>
       </c>
       <c r="C16" t="n">
-        <v>398.76</v>
+        <v>585.3076923076923</v>
       </c>
       <c r="D16" t="n">
-        <v>413.0909090909091</v>
+        <v>507.2608695652174</v>
       </c>
       <c r="E16" t="n">
-        <v>412.2352941176471</v>
+        <v>477.0869565217391</v>
       </c>
       <c r="F16" t="n">
-        <v>410.3076923076923</v>
+        <v>560.6799999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>412.9032258064516</v>
+        <v>483.2</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>6.1875</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>2.375</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>3.3125</v>
       </c>
       <c r="K16" t="n">
-        <v>1.375</v>
+        <v>2.8125</v>
       </c>
       <c r="L16" t="n">
         <v>1.375</v>
       </c>
       <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.375</v>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>1.625</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1505,48 +3244,159 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>302.4684684684685</v>
+        <v>1365.616161616162</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-24</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>849.6900580976915</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.2550969077232967</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.2112833116283052</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.2083996135109389</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>405.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>457.75</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>486.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>518.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>643.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>352</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>466</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>522.6</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>566</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>633.2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>480.1666666666667</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>536.8</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>570.4</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>628.2</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>732</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>468.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>537.25</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>645.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>319</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>423.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>469.2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>549.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>654.6</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>399</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>472.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>535</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>611.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>785.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="n">
-        <v>467.3571428571428</v>
+        <v>384.5555555555555</v>
       </c>
       <c r="C17" t="n">
-        <v>491.0384615384615</v>
+        <v>398.76</v>
       </c>
       <c r="D17" t="n">
-        <v>465.6875</v>
+        <v>413.0909090909091</v>
       </c>
       <c r="E17" t="n">
-        <v>459.625</v>
+        <v>412.2352941176471</v>
       </c>
       <c r="F17" t="n">
-        <v>555.8846153846154</v>
+        <v>410.3076923076923</v>
       </c>
       <c r="G17" t="n">
-        <v>539.9545454545455</v>
+        <v>412.9032258064516</v>
       </c>
       <c r="H17" t="n">
         <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4375</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3125</v>
+        <v>1.375</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1555,10 +3405,10 @@
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4375</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1571,60 +3421,171 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1180.727272727273</v>
+        <v>302.4684684684685</v>
+      </c>
+      <c r="U17" t="n">
+        <v>28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-213.457635050002</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4143057163687305</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.002857738670329376</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1640309838703093</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>291</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>333</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>400.1428571428572</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>440.2857142857143</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>471.7142857142857</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>309</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>392.25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>450.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>502.2</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>298.8</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>397.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>434.2</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>517.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>383.6666666666667</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>417.6666666666667</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>437.3333333333333</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>334.5714285714286</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>376.1666666666667</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>452.1666666666667</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>500.1666666666667</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>325</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>411.6</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>448</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>496.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="n">
-        <v>511.1538461538461</v>
+        <v>467.3571428571428</v>
       </c>
       <c r="C18" t="n">
-        <v>484.8571428571428</v>
+        <v>491.0384615384615</v>
       </c>
       <c r="D18" t="n">
-        <v>504.9166666666667</v>
+        <v>465.6875</v>
       </c>
       <c r="E18" t="n">
-        <v>478.6086956521739</v>
+        <v>459.625</v>
       </c>
       <c r="F18" t="n">
-        <v>476.9090909090909</v>
+        <v>555.8846153846154</v>
       </c>
       <c r="G18" t="n">
-        <v>514.125</v>
+        <v>539.9545454545455</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1875</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>5.25</v>
+        <v>6.4375</v>
       </c>
       <c r="J18" t="n">
-        <v>5.1875</v>
+        <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5</v>
+        <v>2.3125</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>2.4375</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1637,126 +3598,348 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>513.2403846153846</v>
+        <v>1180.727272727273</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>74</v>
+      </c>
+      <c r="W18" t="n">
+        <v>65</v>
+      </c>
+      <c r="X18" t="n">
+        <v>664.8011692088025</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.07775039038085707</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.5092599585867341</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.5671249853316656</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>344</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>412.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>450</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>623.1666666666666</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>329.4285714285714</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>408.8333333333333</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>465</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>506</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>616.7142857142857</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>328.3333333333333</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>501.8</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>575.2</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>661.2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>401.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>473</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>519.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>578.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>456</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>536</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>637.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>782.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>430.3333333333333</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>549</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>604.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>715.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" t="n">
-        <v>473.0416666666667</v>
+        <v>511.1538461538461</v>
       </c>
       <c r="C19" t="n">
-        <v>495.625</v>
+        <v>484.8571428571428</v>
       </c>
       <c r="D19" t="n">
-        <v>493.44</v>
+        <v>504.9166666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>427.08</v>
+        <v>478.6086956521739</v>
       </c>
       <c r="F19" t="n">
-        <v>471.1304347826087</v>
+        <v>476.9090909090909</v>
       </c>
       <c r="G19" t="n">
-        <v>564.76</v>
+        <v>514.125</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5.1875</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>5.25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.125</v>
+        <v>5.1875</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1875</v>
+        <v>2.5</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.125</v>
+        <v>2.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5625</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.625</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>267.9716981132075</v>
+        <v>513.2403846153846</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-2.685718903085785</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.3768487911154049</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.09775528073539708</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.07221075363830989</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>388</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>473.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>529.4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>560.2</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>629.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>467.4</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>494.75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>524.6</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>628.2</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>354.6</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>424.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>509.25</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>551</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>617.75</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>360</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>441.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>484</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>529</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>581.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>375</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>459.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>506.25</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>573.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>655</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>336</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>393.25</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>467.75</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>547.25</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>635.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" t="n">
-        <v>528.5599999999999</v>
+        <v>473.0416666666667</v>
       </c>
       <c r="C20" t="n">
-        <v>491</v>
+        <v>495.625</v>
       </c>
       <c r="D20" t="n">
-        <v>578.3913043478261</v>
+        <v>493.44</v>
       </c>
       <c r="E20" t="n">
-        <v>542.96</v>
+        <v>427.08</v>
       </c>
       <c r="F20" t="n">
-        <v>506.28</v>
+        <v>471.1304347826087</v>
       </c>
       <c r="G20" t="n">
-        <v>569.9642857142857</v>
+        <v>564.76</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5625</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>2.375</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>2.375</v>
+        <v>3.125</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9375</v>
+        <v>2.1875</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9375</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>2.3125</v>
+        <v>2.125</v>
       </c>
       <c r="N20" t="n">
-        <v>4.625</v>
+        <v>5.5625</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5625</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1765,64 +3948,175 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>399.7090909090909</v>
+        <v>267.9716981132075</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-46</v>
+      </c>
+      <c r="V20" t="n">
+        <v>71</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-24</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-247.9544054052629</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.4104371906997899</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.4553918954662598</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.1896357245547947</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>396.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>429.75</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>516.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>677.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>333.6</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>407.8</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>574</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>670.4</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>333.2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>410</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>456.75</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>561.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>709</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>376.8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>399.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>448.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>582.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>465</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>511.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>651.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>849.4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>326</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>391</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>470.6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>530.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>633.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" t="n">
-        <v>386.0344827586207</v>
+        <v>528.5599999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>380.6428571428572</v>
+        <v>491</v>
       </c>
       <c r="D21" t="n">
-        <v>402.4642857142857</v>
+        <v>578.3913043478261</v>
       </c>
       <c r="E21" t="n">
-        <v>394.9166666666667</v>
+        <v>542.96</v>
       </c>
       <c r="F21" t="n">
-        <v>429.2592592592592</v>
+        <v>506.28</v>
       </c>
       <c r="G21" t="n">
-        <v>395.9565217391304</v>
+        <v>569.9642857142857</v>
       </c>
       <c r="H21" t="n">
-        <v>6.625</v>
+        <v>4.5625</v>
       </c>
       <c r="I21" t="n">
-        <v>6.125</v>
+        <v>2.375</v>
       </c>
       <c r="J21" t="n">
-        <v>5.3125</v>
+        <v>2.375</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1875</v>
+        <v>1.9375</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>1.9375</v>
       </c>
       <c r="M21" t="n">
-        <v>1.875</v>
+        <v>2.3125</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8125</v>
+        <v>4.625</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8125</v>
+        <v>2.5625</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1875</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1835,64 +4129,175 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>289.9816513761468</v>
+        <v>399.7090909090909</v>
+      </c>
+      <c r="U21" t="n">
+        <v>14</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-116.2170126093795</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.1418416462293147</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.08821141050085475</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.164751907311412</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>416.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>469.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>533</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>721</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>456</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>518.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>563</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>634</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>719.6</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>455</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>497.6</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>525.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>605.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>494.6</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>530.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>580</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>657.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>438.8333333333333</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>533.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>575.3333333333334</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>615.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>688.1666666666666</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>453</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>554</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>654.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" t="n">
-        <v>343.1904761904762</v>
+        <v>386.0344827586207</v>
       </c>
       <c r="C22" t="n">
-        <v>339.9230769230769</v>
+        <v>380.6428571428572</v>
       </c>
       <c r="D22" t="n">
-        <v>357.2592592592592</v>
+        <v>402.4642857142857</v>
       </c>
       <c r="E22" t="n">
-        <v>374.16</v>
+        <v>394.9166666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>383.3478260869565</v>
+        <v>429.2592592592592</v>
       </c>
       <c r="G22" t="n">
-        <v>343.6818181818182</v>
+        <v>395.9565217391304</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6875</v>
+        <v>6.625</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9375</v>
+        <v>6.125</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9375</v>
+        <v>5.3125</v>
       </c>
       <c r="K22" t="n">
-        <v>1.125</v>
+        <v>1.1875</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>4.0625</v>
+        <v>1.875</v>
       </c>
       <c r="N22" t="n">
-        <v>5.125</v>
+        <v>5.8125</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9375</v>
+        <v>2.8125</v>
       </c>
       <c r="P22" t="n">
-        <v>3.5</v>
+        <v>3.1875</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -1901,126 +4306,348 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>263.4081632653061</v>
+        <v>289.9816513761468</v>
+      </c>
+      <c r="U22" t="n">
+        <v>9</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>49</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-225.9444521423237</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.1258514556068817</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-0.07875484850692986</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.7532878064543831</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>300.6666666666667</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>342.3333333333333</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>411.1666666666667</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>292.8333333333333</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>333.2</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>409.8333333333333</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>464</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>511.1666666666667</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>313.3333333333333</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>343</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>372.3333333333333</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>410.2</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>463</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>328</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>354</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>489</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>320.2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>412.75</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>509.4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>336.1666666666667</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>425</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>464.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>527.6666666666666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" t="n">
-        <v>419</v>
+        <v>350.55</v>
       </c>
       <c r="C23" t="n">
-        <v>422.9259259259259</v>
+        <v>339.9230769230769</v>
       </c>
       <c r="D23" t="n">
-        <v>468.8846153846154</v>
+        <v>363.5</v>
       </c>
       <c r="E23" t="n">
-        <v>429.6956521739131</v>
+        <v>374.16</v>
       </c>
       <c r="F23" t="n">
-        <v>479.375</v>
+        <v>371.1818181818182</v>
       </c>
       <c r="G23" t="n">
-        <v>478.08</v>
+        <v>343.6818181818182</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5.6875</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5625</v>
+        <v>2.9375</v>
       </c>
       <c r="J23" t="n">
-        <v>5.6875</v>
+        <v>3.9375</v>
       </c>
       <c r="K23" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.9375</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.9375</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4.625</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6.0625</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.1875</v>
-      </c>
       <c r="P23" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>288.5462962962963</v>
+        <v>263.4081632653061</v>
+      </c>
+      <c r="U23" t="n">
+        <v>24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-20</v>
+      </c>
+      <c r="W23" t="n">
+        <v>31</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-252.5179402531643</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.2540133077211894</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.2774513564272423</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.4203090115354732</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>228.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>322.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>513.25</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>270.1666666666667</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>409</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>245.8333333333333</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>297.4</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>341.2</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>377.4</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>456.6</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>410.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>485.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>322</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>449.8</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>287</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>330.75</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>366.75</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>456</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" t="n">
-        <v>478.0952380952381</v>
+        <v>419</v>
       </c>
       <c r="C24" t="n">
-        <v>478.1739130434783</v>
+        <v>422.9259259259259</v>
       </c>
       <c r="D24" t="n">
-        <v>445.5</v>
+        <v>468.8846153846154</v>
       </c>
       <c r="E24" t="n">
-        <v>490.3103448275862</v>
+        <v>429.6956521739131</v>
       </c>
       <c r="F24" t="n">
-        <v>469.4347826086956</v>
+        <v>479.375</v>
       </c>
       <c r="G24" t="n">
-        <v>494.5</v>
+        <v>478.08</v>
       </c>
       <c r="H24" t="n">
-        <v>5.875</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
+        <v>3.5625</v>
+      </c>
+      <c r="J24" t="n">
         <v>5.6875</v>
       </c>
-      <c r="J24" t="n">
-        <v>5</v>
-      </c>
       <c r="K24" t="n">
-        <v>1.375</v>
+        <v>1.9375</v>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.9375</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>4.625</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1875</v>
+        <v>6.0625</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3125</v>
+        <v>2.1875</v>
       </c>
       <c r="P24" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2033,57 +4660,168 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>576.5436893203884</v>
+        <v>288.5462962962963</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11</v>
+      </c>
+      <c r="V24" t="n">
+        <v>9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>56</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-227.3798072221741</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.1616066465893992</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.1416559216688784</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.8332292404704101</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>324.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>428</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>454.6</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>506.8333333333333</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>394.3333333333333</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>447.6</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>491.4</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>559.2</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>311</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>427</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>475.8</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>528.6666666666666</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>392</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>418.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>447.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>528.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>437.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>484</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>507</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>577.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>416.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>453.4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>483.75</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>506</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>537.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" t="n">
-        <v>659.6296296296297</v>
+        <v>478.0952380952381</v>
       </c>
       <c r="C25" t="n">
-        <v>704.75</v>
+        <v>478.1739130434783</v>
       </c>
       <c r="D25" t="n">
-        <v>656.4074074074074</v>
+        <v>445.5</v>
       </c>
       <c r="E25" t="n">
-        <v>651.04</v>
+        <v>490.3103448275862</v>
       </c>
       <c r="F25" t="n">
-        <v>690.72</v>
+        <v>469.4347826086956</v>
       </c>
       <c r="G25" t="n">
-        <v>631.08</v>
+        <v>494.5</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9375</v>
+        <v>5.875</v>
       </c>
       <c r="I25" t="n">
-        <v>3.9375</v>
+        <v>5.6875</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9375</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>4.0625</v>
+        <v>1.375</v>
       </c>
       <c r="L25" t="n">
-        <v>4.0625</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>4.0625</v>
+        <v>2.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5625</v>
+        <v>5.1875</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4375</v>
+        <v>4.3125</v>
       </c>
       <c r="P25" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
         <v>21</v>
@@ -2095,64 +4833,175 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>340.4036697247706</v>
+        <v>576.5436893203884</v>
+      </c>
+      <c r="U25" t="n">
+        <v>12</v>
+      </c>
+      <c r="V25" t="n">
+        <v>49</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>60.61758580191793</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.1396685017948061</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.621394560464485</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.117578045856188</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>432.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>543.75</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>582.25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>303</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>426.6666666666667</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>480.3333333333333</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>521.6666666666666</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>543.3333333333334</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>384.8</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>410.75</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>478</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>531</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>583.4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>373.3333333333333</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>446.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>467.4</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>534.1666666666666</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>626.3333333333334</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>397.8571428571428</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>456.2857142857143</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>502.1666666666667</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>531.5714285714286</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>585.7142857142857</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>426.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>462</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>517</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>564</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" t="n">
-        <v>532.2083333333334</v>
+        <v>659.6296296296297</v>
       </c>
       <c r="C26" t="n">
-        <v>634.2692307692307</v>
+        <v>704.75</v>
       </c>
       <c r="D26" t="n">
-        <v>533.2</v>
+        <v>656.4074074074074</v>
       </c>
       <c r="E26" t="n">
-        <v>614.448275862069</v>
+        <v>651.04</v>
       </c>
       <c r="F26" t="n">
-        <v>556.5185185185185</v>
+        <v>690.72</v>
       </c>
       <c r="G26" t="n">
-        <v>495</v>
+        <v>631.08</v>
       </c>
       <c r="H26" t="n">
-        <v>6.75</v>
+        <v>3.9375</v>
       </c>
       <c r="I26" t="n">
+        <v>3.9375</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.9375</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.5625</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.4375</v>
+      </c>
+      <c r="P26" t="n">
         <v>3.5</v>
       </c>
-      <c r="J26" t="n">
-        <v>3.6875</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.8125</v>
-      </c>
-      <c r="N26" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.125</v>
-      </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2165,39 +5014,150 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>515.9909090909091</v>
+        <v>340.4036697247706</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-9</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-25</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-14</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-175.5224337936998</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.05279761750263385</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.2107274113598717</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.07895965242125171</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>466.1666666666667</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>599.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>630.4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>716.8</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>880</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>525</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>601.4</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>656.4</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>685.2</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>809.6666666666666</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>497.4</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>590.6</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>678.25</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>809.6</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>942.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>475</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>542.6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>613.4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>708.2</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>916</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>446.8</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>561.8</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>713</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>818.6</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>499.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>571.4</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>677</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>727.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>978.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" t="n">
-        <v>469.8260869565217</v>
+        <v>532.2083333333334</v>
       </c>
       <c r="C27" t="n">
-        <v>591.0909090909091</v>
+        <v>634.2692307692307</v>
       </c>
       <c r="D27" t="n">
-        <v>533.6666666666666</v>
+        <v>533.2</v>
       </c>
       <c r="E27" t="n">
-        <v>502.7692307692308</v>
+        <v>614.448275862069</v>
       </c>
       <c r="F27" t="n">
-        <v>617.5384615384615</v>
+        <v>556.5185185185185</v>
       </c>
       <c r="G27" t="n">
-        <v>482.962962962963</v>
+        <v>495</v>
       </c>
       <c r="H27" t="n">
-        <v>6.375</v>
+        <v>6.75</v>
       </c>
       <c r="I27" t="n">
-        <v>6.3125</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
-        <v>6.5</v>
+        <v>3.6875</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -2206,19 +5166,19 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2.8125</v>
       </c>
       <c r="N27" t="n">
-        <v>1.125</v>
+        <v>6.625</v>
       </c>
       <c r="O27" t="n">
-        <v>1.125</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.125</v>
+        <v>3.125</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2231,57 +5191,168 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>353.078431372549</v>
+        <v>515.9909090909091</v>
+      </c>
+      <c r="U27" t="n">
+        <v>82</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-38</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-78</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.06480557243867224</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.6677162348182369</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-0.3185066126761822</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.6679987153173076</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>389</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>453.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>509.75</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>614.4</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>690</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>366</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>442.8333333333333</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>530.3333333333334</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>607</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>719.8333333333334</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>504.5</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>593.6</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>640.6</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>690.4</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>768.2</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>462.3333333333333</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>529.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>613</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>655.6666666666666</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>811.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>360</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>422.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>505</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>558.75</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>629</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>390.3333333333333</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>461.8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>563</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>636.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>729.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" t="n">
-        <v>657.4400000000001</v>
+        <v>469.8260869565217</v>
       </c>
       <c r="C28" t="n">
-        <v>572.304347826087</v>
+        <v>591.0909090909091</v>
       </c>
       <c r="D28" t="n">
-        <v>701</v>
+        <v>533.6666666666666</v>
       </c>
       <c r="E28" t="n">
-        <v>660.7857142857143</v>
+        <v>502.7692307692308</v>
       </c>
       <c r="F28" t="n">
-        <v>555.1363636363636</v>
+        <v>617.5384615384615</v>
       </c>
       <c r="G28" t="n">
-        <v>649.8846153846154</v>
+        <v>482.962962962963</v>
       </c>
       <c r="H28" t="n">
-        <v>6.5625</v>
+        <v>6.375</v>
       </c>
       <c r="I28" t="n">
-        <v>6.375</v>
+        <v>6.3125</v>
       </c>
       <c r="J28" t="n">
-        <v>5.875</v>
+        <v>6.5</v>
       </c>
       <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
         <v>1.125</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.75</v>
-      </c>
       <c r="O28" t="n">
-        <v>2.4375</v>
+        <v>1.125</v>
       </c>
       <c r="P28" t="n">
-        <v>3.625</v>
+        <v>1.125</v>
       </c>
       <c r="Q28" t="n">
         <v>21</v>
@@ -2297,60 +5368,171 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>523.074074074074</v>
+        <v>353.078431372549</v>
+      </c>
+      <c r="U28" t="n">
+        <v>33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-51</v>
+      </c>
+      <c r="W28" t="n">
+        <v>26</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-162.8476721459214</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.2444630616302982</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-0.3492695031819421</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.1415312646256618</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>390</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>639.8</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>472</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>593</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>686.8</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>365</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>489</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>575.75</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>679.25</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>840.6</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>312.6666666666667</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>404.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>509.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>605</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>720</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>307.8333333333333</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>382.2</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>420.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>528</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>756.3333333333334</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>392.6666666666667</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>500.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>602.2</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>738</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>899.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" t="n">
-        <v>596.25</v>
+        <v>657.4400000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>569.8947368421053</v>
+        <v>572.304347826087</v>
       </c>
       <c r="D29" t="n">
-        <v>603.5555555555555</v>
+        <v>701</v>
       </c>
       <c r="E29" t="n">
-        <v>578.2727272727273</v>
+        <v>660.7857142857143</v>
       </c>
       <c r="F29" t="n">
-        <v>581.6190476190476</v>
+        <v>555.1363636363636</v>
       </c>
       <c r="G29" t="n">
-        <v>608.8695652173913</v>
+        <v>649.8846153846154</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6875</v>
+        <v>6.5625</v>
       </c>
       <c r="I29" t="n">
-        <v>5.6875</v>
+        <v>6.375</v>
       </c>
       <c r="J29" t="n">
-        <v>5.125</v>
+        <v>5.875</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="L29" t="n">
-        <v>1.125</v>
+        <v>1.375</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0625</v>
+        <v>2.625</v>
       </c>
       <c r="N29" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="O29" t="n">
-        <v>6.125</v>
+        <v>2.4375</v>
       </c>
       <c r="P29" t="n">
-        <v>5.6875</v>
+        <v>3.625</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2363,60 +5545,171 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>632.1862745098039</v>
+        <v>523.074074074074</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-51</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-17</v>
+      </c>
+      <c r="X29" t="n">
+        <v>7.147970555603592</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.02452722484885311</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-0.3783471066022847</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.1547169859633948</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>600.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>652.8</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>689.8</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>841.4</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>527</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>693</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>757</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>439.8</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>503.5</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>556.6</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>622.75</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>735.2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>471.6666666666667</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>572.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>642.8333333333334</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>738.4</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>876.8333333333334</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>517.8333333333334</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>581</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>613.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>699.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>864</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>511.75</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>543.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>583.75</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>708</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" t="n">
-        <v>399.3461538461539</v>
+        <v>596.25</v>
       </c>
       <c r="C30" t="n">
-        <v>402.625</v>
+        <v>569.8947368421053</v>
       </c>
       <c r="D30" t="n">
-        <v>389.28</v>
+        <v>603.5555555555555</v>
       </c>
       <c r="E30" t="n">
-        <v>439.16</v>
+        <v>578.2727272727273</v>
       </c>
       <c r="F30" t="n">
-        <v>483.375</v>
+        <v>581.6190476190476</v>
       </c>
       <c r="G30" t="n">
-        <v>417.3846153846154</v>
+        <v>608.8695652173913</v>
       </c>
       <c r="H30" t="n">
-        <v>5.875</v>
+        <v>5.6875</v>
       </c>
       <c r="I30" t="n">
-        <v>5.625</v>
+        <v>5.6875</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4375</v>
+        <v>5.125</v>
       </c>
       <c r="K30" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.6875</v>
+        <v>1.125</v>
       </c>
       <c r="M30" t="n">
-        <v>1.75</v>
+        <v>1.0625</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8125</v>
+        <v>6.25</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8125</v>
+        <v>6.125</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4375</v>
+        <v>5.6875</v>
       </c>
       <c r="Q30" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2429,60 +5722,171 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>1027.283018867925</v>
+        <v>632.1862745098039</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-18</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>12</v>
+      </c>
+      <c r="X30" t="n">
+        <v>116.2601709913334</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.1051816487400204</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.03791067261957781</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.05259349583907061</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>479.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>583.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>701.6</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>858.2</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>437.3333333333333</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>516.2</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>649.8</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>810</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>479.6666666666667</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>648</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>922.25</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>410</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>492.25</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>539.25</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>641.75</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>795.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>418.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>538.25</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>689.25</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>385</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>527.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>610.25</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>964.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
-        <v>480</v>
+        <v>399.3461538461539</v>
       </c>
       <c r="C31" t="n">
-        <v>479.5925925925926</v>
+        <v>402.625</v>
       </c>
       <c r="D31" t="n">
-        <v>484.9615384615385</v>
+        <v>389.28</v>
       </c>
       <c r="E31" t="n">
-        <v>508.2692307692308</v>
+        <v>439.16</v>
       </c>
       <c r="F31" t="n">
-        <v>492.8846153846154</v>
+        <v>483.375</v>
       </c>
       <c r="G31" t="n">
-        <v>483.7692307692308</v>
+        <v>417.3846153846154</v>
       </c>
       <c r="H31" t="n">
-        <v>6.5625</v>
+        <v>5.875</v>
       </c>
       <c r="I31" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.4375</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.8125</v>
+      </c>
+      <c r="O31" t="n">
         <v>2.8125</v>
       </c>
-      <c r="J31" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.5625</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.375</v>
-      </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>2.4375</v>
       </c>
       <c r="Q31" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2495,60 +5899,171 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>566.3873873873874</v>
+        <v>1027.283018867925</v>
+      </c>
+      <c r="U31" t="n">
+        <v>40</v>
+      </c>
+      <c r="V31" t="n">
+        <v>28</v>
+      </c>
+      <c r="W31" t="n">
+        <v>81</v>
+      </c>
+      <c r="X31" t="n">
+        <v>511.3569153494545</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.4803254647451797</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.3599251046169005</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.8759718283267917</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>409.6</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>533.6</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>278.6</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>342.6</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>433</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>509.8</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>403.25</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>451.6</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>334.4</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>405</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>443.8</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>534.8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>320.6666666666667</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>379</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>422.4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>465</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>519.2</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>423</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>473</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>514.4</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>636.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B32" t="n">
-        <v>532.3333333333334</v>
+        <v>480</v>
       </c>
       <c r="C32" t="n">
-        <v>599.6521739130435</v>
+        <v>479.5925925925926</v>
       </c>
       <c r="D32" t="n">
-        <v>541.5833333333334</v>
+        <v>484.9615384615385</v>
       </c>
       <c r="E32" t="n">
-        <v>537</v>
+        <v>508.2692307692308</v>
       </c>
       <c r="F32" t="n">
-        <v>616.7727272727273</v>
+        <v>492.8846153846154</v>
       </c>
       <c r="G32" t="n">
-        <v>579.1153846153846</v>
+        <v>483.7692307692308</v>
       </c>
       <c r="H32" t="n">
-        <v>5.3125</v>
+        <v>6.5625</v>
       </c>
       <c r="I32" t="n">
-        <v>5.25</v>
+        <v>2.8125</v>
       </c>
       <c r="J32" t="n">
-        <v>5.3125</v>
+        <v>6.625</v>
       </c>
       <c r="K32" t="n">
-        <v>5.125</v>
+        <v>3.5625</v>
       </c>
       <c r="L32" t="n">
-        <v>5.125</v>
+        <v>2.625</v>
       </c>
       <c r="M32" t="n">
-        <v>5.125</v>
+        <v>3.875</v>
       </c>
       <c r="N32" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="O32" t="n">
-        <v>5.25</v>
+        <v>2.375</v>
       </c>
       <c r="P32" t="n">
-        <v>5.125</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2561,60 +6076,171 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>909.2095238095238</v>
+        <v>566.3873873873874</v>
+      </c>
+      <c r="U32" t="n">
+        <v>28</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>13</v>
+      </c>
+      <c r="X32" t="n">
+        <v>50.46128386891701</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.3520350520908095</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.01557191576838428</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.1864242479367628</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>380.8333333333333</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>433.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>514.8</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>607</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>372.6666666666667</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>446.6</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>485.2</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>528.4</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>614.4</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>399.8333333333333</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>438.4</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>472.2</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>511.8</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>573</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>418.3333333333333</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>462.2</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>549.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>625</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>465.6</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>491.8</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>556.8</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>391.1666666666667</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>461.2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>504.4</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>539.6</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>588.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" t="n">
-        <v>422.2916666666667</v>
+        <v>532.3333333333334</v>
       </c>
       <c r="C33" t="n">
-        <v>475.0740740740741</v>
+        <v>599.6521739130435</v>
       </c>
       <c r="D33" t="n">
-        <v>471.8260869565217</v>
+        <v>541.5833333333334</v>
       </c>
       <c r="E33" t="n">
-        <v>460.551724137931</v>
+        <v>537</v>
       </c>
       <c r="F33" t="n">
-        <v>475.5769230769231</v>
+        <v>616.7727272727273</v>
       </c>
       <c r="G33" t="n">
-        <v>462</v>
+        <v>579.1153846153846</v>
       </c>
       <c r="H33" t="n">
-        <v>6.4375</v>
+        <v>5.3125</v>
       </c>
       <c r="I33" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J33" t="n">
         <v>5.3125</v>
       </c>
-      <c r="J33" t="n">
-        <v>5.5625</v>
-      </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>5.125</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>5.125</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>5.125</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3125</v>
+        <v>5.25</v>
       </c>
       <c r="O33" t="n">
-        <v>1.8125</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.75</v>
+        <v>5.125</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2627,60 +6253,171 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>410.5982142857143</v>
+        <v>909.2095238095238</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>38</v>
+      </c>
+      <c r="W33" t="n">
+        <v>17</v>
+      </c>
+      <c r="X33" t="n">
+        <v>393.2834202910534</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.05888619769610783</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.2997794434593292</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.1107702212293784</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>464.2</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>499</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>530.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>569</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>616</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>430.4</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>478</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>526.25</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>601.4</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>668.8</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>378</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>582.4</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>661.75</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>854.4</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>478.8333333333333</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>512.8</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>577.6666666666666</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>678.1666666666666</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>430.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>486.2</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>538.4</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>638.4</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>831.8</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>444.6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>550</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>610</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>697</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>783.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="n">
-        <v>492.1111111111111</v>
+        <v>422.2916666666667</v>
       </c>
       <c r="C34" t="n">
-        <v>475.4814814814815</v>
+        <v>475.0740740740741</v>
       </c>
       <c r="D34" t="n">
-        <v>452.1481481481482</v>
+        <v>471.8260869565217</v>
       </c>
       <c r="E34" t="n">
-        <v>501.0740740740741</v>
+        <v>460.551724137931</v>
       </c>
       <c r="F34" t="n">
-        <v>502.12</v>
+        <v>475.5769230769231</v>
       </c>
       <c r="G34" t="n">
-        <v>515.6296296296297</v>
+        <v>462</v>
       </c>
       <c r="H34" t="n">
-        <v>2.125</v>
+        <v>6.4375</v>
       </c>
       <c r="I34" t="n">
-        <v>3.0625</v>
+        <v>5.3125</v>
       </c>
       <c r="J34" t="n">
-        <v>4.8125</v>
+        <v>5.5625</v>
       </c>
       <c r="K34" t="n">
-        <v>2.0625</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.9375</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5625</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
+        <v>5.3125</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.8125</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.875</v>
-      </c>
       <c r="P34" t="n">
-        <v>1.8125</v>
+        <v>4.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2689,64 +6426,175 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>503.0446428571428</v>
+        <v>410.5982142857143</v>
+      </c>
+      <c r="U34" t="n">
+        <v>38</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-10</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-105.3278892327561</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.7931785754965173</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-0.1702075628535099</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.006663674254424308</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>396</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>491.8</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>378</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>475</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>505</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>563.4</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>364.3333333333333</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>428</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>509.2</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>608</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>434.6666666666667</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>462.4</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>485.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>527</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>396.5714285714286</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>449.6666666666667</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>467.3333333333333</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>484.3333333333333</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>523</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>402.1666666666667</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>451.8</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>507.6</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>555.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" t="n">
-        <v>569.7142857142857</v>
+        <v>492.1111111111111</v>
       </c>
       <c r="C35" t="n">
-        <v>587.12</v>
+        <v>475.4814814814815</v>
       </c>
       <c r="D35" t="n">
-        <v>594.3333333333334</v>
+        <v>452.1481481481482</v>
       </c>
       <c r="E35" t="n">
-        <v>599.4736842105264</v>
+        <v>501.0740740740741</v>
       </c>
       <c r="F35" t="n">
-        <v>655.2916666666666</v>
+        <v>502.12</v>
       </c>
       <c r="G35" t="n">
-        <v>553</v>
+        <v>515.6296296296297</v>
       </c>
       <c r="H35" t="n">
-        <v>6.6875</v>
+        <v>2.125</v>
       </c>
       <c r="I35" t="n">
-        <v>5.25</v>
+        <v>3.0625</v>
       </c>
       <c r="J35" t="n">
-        <v>3.9375</v>
+        <v>4.8125</v>
       </c>
       <c r="K35" t="n">
-        <v>1.6875</v>
+        <v>2.0625</v>
       </c>
       <c r="L35" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.5625</v>
+      </c>
+      <c r="N35" t="n">
         <v>1.8125</v>
       </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>6.75</v>
-      </c>
       <c r="O35" t="n">
-        <v>2.125</v>
+        <v>1.875</v>
       </c>
       <c r="P35" t="n">
-        <v>2.125</v>
+        <v>1.8125</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2755,134 +6603,356 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="T35" t="n">
-        <v>590.7244897959183</v>
+        <v>503.0446428571428</v>
+      </c>
+      <c r="U35" t="n">
+        <v>9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>63</v>
+      </c>
+      <c r="W35" t="n">
+        <v>27</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-12.88146066132765</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.09163820709658176</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.6825012028444949</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.2512545962985255</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>344.8333333333333</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>442.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>470</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>550.4</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>650.6666666666666</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>410.4</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>502.2</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>540.8333333333334</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>313.6666666666667</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>430.2</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>484.2</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>528.6</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>623.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>411.3333333333333</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>460.4</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>492.2</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>520.4</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>616</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>376.3333333333333</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>465.2</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>507</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>566.8</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>661.5</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>458.4</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>503</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>554.8</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>621.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" t="n">
-        <v>399.88</v>
+        <v>569.7142857142857</v>
       </c>
       <c r="C36" t="n">
-        <v>434</v>
+        <v>587.12</v>
       </c>
       <c r="D36" t="n">
-        <v>401.2903225806452</v>
+        <v>594.3333333333334</v>
       </c>
       <c r="E36" t="n">
-        <v>434</v>
+        <v>599.4736842105264</v>
       </c>
       <c r="F36" t="n">
-        <v>433.5925925925926</v>
+        <v>655.2916666666666</v>
       </c>
       <c r="G36" t="n">
-        <v>427.6190476190476</v>
+        <v>553</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>6.6875</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>3.9375</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>1.6875</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>1.8125</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
         <v>6.75</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>2.125</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>2.125</v>
       </c>
       <c r="Q36" t="n">
+        <v>21</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>590.7244897959183</v>
+      </c>
+      <c r="U36" t="n">
         <v>30</v>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="T36" t="n">
-        <v>329.8165137614679</v>
+      <c r="V36" t="n">
+        <v>-41</v>
+      </c>
+      <c r="W36" t="n">
+        <v>68</v>
+      </c>
+      <c r="X36" t="n">
+        <v>74.79838627744789</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.2404545808263196</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-0.3083908410337818</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.4779756971344722</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>428.6666666666667</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>524.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>564.3333333333334</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>610.4</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>719.6666666666666</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>541</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>590</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>668.5</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>808.5</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>435.8</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>515.8</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>553.2</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>648.4</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>782.4</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>423</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>523</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>580.6666666666666</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>664</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>802</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>398</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>472.6</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>537.2</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>614.4</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>742.8</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>580.6</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>657</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>706.6</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>880.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" t="n">
-        <v>628.1034482758621</v>
+        <v>399.88</v>
       </c>
       <c r="C37" t="n">
-        <v>811.7037037037037</v>
+        <v>434</v>
       </c>
       <c r="D37" t="n">
-        <v>621.8571428571429</v>
+        <v>401.2903225806452</v>
       </c>
       <c r="E37" t="n">
-        <v>627.3636363636364</v>
+        <v>434</v>
       </c>
       <c r="F37" t="n">
-        <v>723.7391304347826</v>
+        <v>433.5925925925926</v>
       </c>
       <c r="G37" t="n">
-        <v>655.1935483870968</v>
+        <v>427.6190476190476</v>
       </c>
       <c r="H37" t="n">
-        <v>6.375</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>6.375</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>1.3125</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1.625</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>6.0625</v>
+        <v>6.75</v>
       </c>
       <c r="O37" t="n">
-        <v>5.9375</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>4.75</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -2891,60 +6961,171 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>1058.091743119266</v>
+        <v>329.8165137614679</v>
+      </c>
+      <c r="U37" t="n">
+        <v>34</v>
+      </c>
+      <c r="V37" t="n">
+        <v>26</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-186.1095897570025</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.4599308313818795</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.3828796725474692</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-0.005715474002673982</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>397.4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>439</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>520</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>319.8571428571428</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>357.6666666666667</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>431.3333333333333</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>517.6666666666666</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>326.3333333333333</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>394.4</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>465.8</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>545.1666666666666</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>350.6666666666667</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>442</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>469.2</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>521.3333333333334</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>345.6</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>400</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>432</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>473.25</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>507.75</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>359</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>433.8</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>467.4</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>501.8333333333333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" t="n">
-        <v>423.9285714285714</v>
+        <v>628.1034482758621</v>
       </c>
       <c r="C38" t="n">
-        <v>462</v>
+        <v>811.7037037037037</v>
       </c>
       <c r="D38" t="n">
-        <v>443.125</v>
+        <v>621.8571428571429</v>
       </c>
       <c r="E38" t="n">
-        <v>420.5833333333333</v>
+        <v>627.3636363636364</v>
       </c>
       <c r="F38" t="n">
-        <v>490.6923076923077</v>
+        <v>723.7391304347826</v>
       </c>
       <c r="G38" t="n">
-        <v>432.5555555555555</v>
+        <v>655.1935483870968</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>6.375</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1875</v>
+        <v>6.375</v>
       </c>
       <c r="J38" t="n">
-        <v>2.1875</v>
+        <v>5.75</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.3125</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1.375</v>
+        <v>1.625</v>
       </c>
       <c r="N38" t="n">
-        <v>6.625</v>
+        <v>6.0625</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>5.9375</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>4.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -2957,64 +7138,175 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>565.8130841121496</v>
+        <v>1058.091743119266</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>33</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-88</v>
+      </c>
+      <c r="X38" t="n">
+        <v>542.1656396007957</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.005726306950301989</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.2450497037715547</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.5319175777480044</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>453.8333333333333</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>562.8333333333334</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>603.4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>687.8333333333334</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>828.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>574</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>590</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>675.75</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>786.75</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>553.3333333333334</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>805</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>914</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1076.333333333333</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>480.4</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>579.75</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>617</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>666.25</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>789.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>463.1428571428572</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>580.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>636.6666666666666</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>737.3333333333334</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>890.3333333333334</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>565.2</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>657.25</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>723.6</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>783</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>888.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" t="n">
-        <v>425.3913043478261</v>
+        <v>423.9285714285714</v>
       </c>
       <c r="C39" t="n">
-        <v>488.75</v>
+        <v>462</v>
       </c>
       <c r="D39" t="n">
-        <v>458.7407407407408</v>
+        <v>443.125</v>
       </c>
       <c r="E39" t="n">
-        <v>455.1538461538461</v>
+        <v>420.5833333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>448.4230769230769</v>
+        <v>490.6923076923077</v>
       </c>
       <c r="G39" t="n">
-        <v>442.6666666666667</v>
+        <v>432.5555555555555</v>
       </c>
       <c r="H39" t="n">
-        <v>4.9375</v>
+        <v>7</v>
       </c>
       <c r="I39" t="n">
-        <v>4.875</v>
+        <v>1.1875</v>
       </c>
       <c r="J39" t="n">
-        <v>5.375</v>
+        <v>2.1875</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1875</v>
+        <v>1.375</v>
       </c>
       <c r="N39" t="n">
-        <v>1.9375</v>
+        <v>6.625</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>4.0625</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3023,139 +7315,649 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>408.254716981132</v>
+        <v>565.8130841121496</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>-11</v>
+      </c>
+      <c r="W39" t="n">
+        <v>29</v>
+      </c>
+      <c r="X39" t="n">
+        <v>49.88698059367914</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-0.05033926906402102</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-0.1692521903735145</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.3748698860796261</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>397</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>417.3333333333333</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>529</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>350.6</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>395.4</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>436.75</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>481.8</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>549.8</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>347.4</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>422.2</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>589.8</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>420.75</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>361.1666666666667</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>418.8</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>444.4</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>458.8</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>483.6666666666667</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>406.1666666666667</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>456.2</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>492.6</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>528.8</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>586.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" t="n">
-        <v>599.1666666666666</v>
+        <v>436.0454545454546</v>
       </c>
       <c r="C40" t="n">
-        <v>640.2962962962963</v>
+        <v>488.75</v>
       </c>
       <c r="D40" t="n">
-        <v>654.76</v>
+        <v>458.7407407407408</v>
       </c>
       <c r="E40" t="n">
-        <v>627.3571428571429</v>
+        <v>455.1538461538461</v>
       </c>
       <c r="F40" t="n">
-        <v>627.8461538461538</v>
+        <v>448.4230769230769</v>
       </c>
       <c r="G40" t="n">
-        <v>594.4400000000001</v>
+        <v>442.6666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>4.9375</v>
       </c>
       <c r="I40" t="n">
-        <v>4.5625</v>
+        <v>4.875</v>
       </c>
       <c r="J40" t="n">
-        <v>5.875</v>
+        <v>5.375</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>1.1875</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>4.1875</v>
       </c>
       <c r="N40" t="n">
-        <v>5.9375</v>
+        <v>1.9375</v>
       </c>
       <c r="O40" t="n">
-        <v>1.375</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.875</v>
+        <v>4.0625</v>
       </c>
       <c r="Q40" t="n">
+        <v>20</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>408.254716981132</v>
+      </c>
+      <c r="U40" t="n">
         <v>19</v>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="T40" t="n">
-        <v>317.4622641509434</v>
+      <c r="V40" t="n">
+        <v>-16</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-40</v>
+      </c>
+      <c r="X40" t="n">
+        <v>-107.6713865373384</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.1824955969247256</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-0.146354166625049</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-0.4850656514764228</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>389</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>448.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>486.75</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>564.4</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>334.6666666666667</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>379</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>416.2</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>527.4</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>627.5</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>454</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>493.75</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>597.8</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>328</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>422.4</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>463.4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>603.6</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>440.25</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>493.2</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>582</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>345.3333333333333</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>406.8</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>459.4</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>488.8</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>562.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" t="n">
-        <v>641.2105263157895</v>
+        <v>599.1666666666666</v>
       </c>
       <c r="C41" t="n">
-        <v>550.28</v>
+        <v>640.2962962962963</v>
       </c>
       <c r="D41" t="n">
-        <v>586.84</v>
+        <v>654.76</v>
       </c>
       <c r="E41" t="n">
-        <v>656.1</v>
+        <v>627.3571428571429</v>
       </c>
       <c r="F41" t="n">
-        <v>625.08</v>
+        <v>627.8461538461538</v>
       </c>
       <c r="G41" t="n">
-        <v>634.1428571428571</v>
+        <v>594.4400000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I41" t="n">
-        <v>1.125</v>
+        <v>4.5625</v>
       </c>
       <c r="J41" t="n">
-        <v>2.25</v>
+        <v>5.875</v>
       </c>
       <c r="K41" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>6.25</v>
+        <v>5.9375</v>
       </c>
       <c r="O41" t="n">
         <v>1.375</v>
       </c>
       <c r="P41" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>19</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>317.4622641509434</v>
+      </c>
+      <c r="U41" t="n">
+        <v>28</v>
+      </c>
+      <c r="V41" t="n">
+        <v>-60</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-12</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-198.463839367527</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.1940070954490909</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-0.3914001680429605</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-0.07106536290866519</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>411.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>498.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>560.75</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>678.4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>839.2</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>448.2</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>511.2</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>620.4</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>749.2</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>944.8</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>401</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>516.2</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>634.6</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>882.6666666666666</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>469.6666666666667</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>547.2</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>615.5</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>684.8</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>815.8333333333334</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>450.6</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>534</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>591.8</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>649.4</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>746.4</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>448.1666666666667</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>548.6</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>610.6</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>678</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>889.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>55</v>
+      </c>
+      <c r="B42" t="n">
+        <v>641.2105263157895</v>
+      </c>
+      <c r="C42" t="n">
+        <v>550.28</v>
+      </c>
+      <c r="D42" t="n">
+        <v>586.84</v>
+      </c>
+      <c r="E42" t="n">
+        <v>656.1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>625.08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>634.1428571428571</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
         <v>20</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="T41" t="n">
+      <c r="T42" t="n">
         <v>580.4554455445544</v>
+      </c>
+      <c r="U42" t="n">
+        <v>15</v>
+      </c>
+      <c r="V42" t="n">
+        <v>47</v>
+      </c>
+      <c r="W42" t="n">
+        <v>75</v>
+      </c>
+      <c r="X42" t="n">
+        <v>64.52934202608401</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.1029112797790023</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.4460071819402938</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.4554311547007729</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>562.25</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>602.3333333333334</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>665</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>866.75</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>532.8</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>575</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>617.6</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>748.6</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>451.2</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>522</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>616</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>787.4</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>452.3333333333333</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>582.6666666666666</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>645.1666666666666</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>719</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>881.3333333333334</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>496</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>581.25</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>630.5</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>709.25</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>788.25</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>389.4</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>524.6</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>620.4</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>718.2</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>872.8</v>
       </c>
     </row>
   </sheetData>
